--- a/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_GPT5.5Generation_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_GPT5.5Generation_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/2 stage/6-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8538C1F6-7E89-E344-91F9-5548C17B2E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37D7356C-0C06-3341-BC32-9AF73D425B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18900" yWindow="-20420" windowWidth="30240" windowHeight="17300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10660,7 +10660,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="25">
-        <f>COUNTIF('Chess Clock'!$A$2:$A$44, A7)</f>
+        <f>COUNTIF('Chess Clock'!$A$2:$A$46, A7)</f>
         <v>2</v>
       </c>
       <c r="C7" s="26">
@@ -10732,7 +10732,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="25">
-        <f>COUNTIF('Chess Clock'!$A$2:$A$44, A9)</f>
+        <f>COUNTIF('Chess Clock'!$A$2:$A$46, A9)</f>
         <v>4</v>
       </c>
       <c r="C9" s="26">
